--- a/data/file_generation/input/data_187/PP01_P_埋点定义_处理后只有dataID和eventname值_-_副本.xlsx
+++ b/data/file_generation/input/data_187/PP01_P_埋点定义_处理后只有dataID和eventname值_-_副本.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/liyanjie1/Desktop/program/data_clean-20260204/cleaned_data/input/data_187/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EBF849A-2E90-8148-B31D-08EB76029199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{423660C5-9261-ED42-9D1E-5237E3AE3B4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="12100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="89">
   <si>
     <t>事件名称</t>
   </si>
@@ -257,9 +257,6 @@
     <t>03000102010000000000000000400006</t>
   </si>
   <si>
-    <t>HU_account_swichting</t>
-  </si>
-  <si>
     <t>662</t>
   </si>
   <si>
@@ -275,9 +272,6 @@
     <t>03000102010000000000000000400003</t>
   </si>
   <si>
-    <t>Hu_Login_Type</t>
-  </si>
-  <si>
     <t>663</t>
   </si>
   <si>
@@ -293,9 +287,6 @@
     <t>03000102010000000000000000400364</t>
   </si>
   <si>
-    <t>Hu_Vehicle_Return_Value</t>
-  </si>
-  <si>
     <t>664</t>
   </si>
   <si>
@@ -306,9 +297,6 @@
   </si>
   <si>
     <t>03000102010000000000000000400000</t>
-  </si>
-  <si>
-    <t>Hu_Vehicle_Activation</t>
   </si>
   <si>
     <t>人员1</t>
@@ -316,6 +304,10 @@
   </si>
   <si>
     <t>人员2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -875,10 +867,10 @@
         <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
         <v>67</v>
@@ -1055,21 +1047,21 @@
         <v>58</v>
       </c>
       <c r="BK2" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:63" s="2" customFormat="1">
       <c r="A3" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>67</v>
@@ -1081,13 +1073,13 @@
         <v>65</v>
       </c>
       <c r="H3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>64</v>
@@ -1102,7 +1094,7 @@
         <v>55</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>56</v>
@@ -1246,21 +1238,21 @@
         <v>58</v>
       </c>
       <c r="BK3" s="2" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:63">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B4" t="s">
         <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
         <v>67</v>
@@ -1272,13 +1264,13 @@
         <v>65</v>
       </c>
       <c r="H4" t="s">
+        <v>78</v>
+      </c>
+      <c r="I4" t="s">
+        <v>79</v>
+      </c>
+      <c r="J4" t="s">
         <v>80</v>
-      </c>
-      <c r="I4" t="s">
-        <v>81</v>
-      </c>
-      <c r="J4" t="s">
-        <v>82</v>
       </c>
       <c r="K4" t="s">
         <v>53</v>
@@ -1293,7 +1285,7 @@
         <v>55</v>
       </c>
       <c r="O4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="P4" t="s">
         <v>56</v>
@@ -1437,21 +1429,21 @@
         <v>58</v>
       </c>
       <c r="BK4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:63">
       <c r="A5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B5" t="s">
         <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
         <v>67</v>
@@ -1463,13 +1455,13 @@
         <v>65</v>
       </c>
       <c r="H5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="J5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K5" t="s">
         <v>64</v>
@@ -1484,7 +1476,7 @@
         <v>55</v>
       </c>
       <c r="O5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="P5" t="s">
         <v>56</v>
@@ -1628,7 +1620,7 @@
         <v>58</v>
       </c>
       <c r="BK5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1802,13 +1794,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8005691D-A164-4A42-B1AC-5EA5A810576A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD61B7C3-CBF0-4103-AE25-67DE4DA4CA37}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1118E989-7464-4070-8B4A-DACA96149AA6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04C6D575-61CF-4F78-9C5B-8F41E4A2D5AA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5350492-72FF-4B87-9801-1B312E225911}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{268A02A7-FFA1-4644-8416-4882A66CA5BD}"/>
 </file>